--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPJ_DAE_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPJ_DAE_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPJ_DAE_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPJ_DAE_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -268,7 +268,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -624,7 +624,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1324,9 +1324,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>27.51</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>68.37</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>64.26000000000001</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45800</v>
+        <v>45801</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>87.37</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>28.57</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45702</v>
+        <v>45703</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>19.83</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>69.95999999999999</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>46075</v>
+        <v>46076</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>25.38</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45857</v>
+        <v>45858</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>83.54000000000001</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>34.02</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>56.43</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>33.5</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>43.7</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>32.9</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>40.57</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>25.48</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>83.45999999999999</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>90.79000000000001</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>4.07</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>94.20999999999999</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>16.15</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>35.83</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>28.16</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>56.25</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>69.25</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45807</v>
+        <v>45808</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>50.55</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>16.92</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>92.84</v>
       </c>
       <c r="AI34" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>45641</v>
+        <v>45642</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>19.87</v>
       </c>
       <c r="AI35" s="5" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>77.78</v>
       </c>
       <c r="AI36" s="5" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="AI38" s="5" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>41.79</v>
       </c>
       <c r="AI39" s="5" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>25.76</v>
       </c>
       <c r="AI40" s="5" t="n">
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -9167,9 +9167,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -9355,7 +9355,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.71875</v>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.7083333333333334</v>
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -9727,7 +9727,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.96875</v>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.9895833333333334</v>
@@ -9918,7 +9918,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.5</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.34375</v>
@@ -10100,7 +10100,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -10287,7 +10287,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.9375</v>
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.96875</v>
@@ -10473,7 +10473,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45711</v>
+        <v>45712</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.3125</v>
@@ -10663,7 +10663,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.75</v>
@@ -10862,7 +10862,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>0.8125</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.8958333333333334</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.7916666666666666</v>
@@ -11206,7 +11206,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.78125</v>
@@ -11234,7 +11234,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.59375</v>
@@ -11424,7 +11424,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.65625</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.6666666666666666</v>
@@ -11805,7 +11805,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.6979166666666666</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.8854166666666666</v>
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -12177,7 +12177,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.6666666666666666</v>
@@ -12364,7 +12364,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.875</v>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.71875</v>
@@ -12550,7 +12550,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.3645833333333333</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.90625</v>
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.8020833333333334</v>
@@ -12927,7 +12927,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.4583333333333333</v>
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.4895833333333333</v>
@@ -13311,7 +13311,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -13505,7 +13505,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.5208333333333334</v>
@@ -13668,7 +13668,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.46875</v>
@@ -13704,7 +13704,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.3020833333333333</v>
@@ -13862,7 +13862,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.4375</v>
@@ -13894,7 +13894,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.90625</v>
@@ -14052,7 +14052,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.9479166666666666</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.5833333333333334</v>
@@ -14243,7 +14243,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.71875</v>
@@ -14275,7 +14275,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.65625</v>
@@ -14438,7 +14438,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.625</v>
@@ -14466,7 +14466,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.3020833333333333</v>
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.4895833333333333</v>
@@ -14661,7 +14661,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.9895833333333334</v>
@@ -14819,7 +14819,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.3541666666666667</v>
@@ -14851,7 +14851,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.96875</v>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -15176,7 +15176,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="AD34" s="8" t="n">
         <v>0.4479166666666667</v>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="AJ34" s="5" t="n">
-        <v>45969</v>
+        <v>45970</v>
       </c>
       <c r="AK34" s="8" t="n">
         <v>0.8541666666666666</v>
@@ -15235,7 +15235,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="AD35" s="8" t="n">
         <v>0.6875</v>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="AJ35" s="5" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="AK35" s="8" t="n">
         <v>0.40625</v>
@@ -15428,7 +15428,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AD36" s="8" t="n">
         <v>0.8541666666666666</v>
@@ -15591,7 +15591,7 @@
         </is>
       </c>
       <c r="AJ36" s="5" t="n">
-        <v>45800</v>
+        <v>45801</v>
       </c>
       <c r="AK36" s="8" t="n">
         <v>0.96875</v>
@@ -15760,7 +15760,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="AD38" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -15791,7 +15791,7 @@
         </is>
       </c>
       <c r="AJ38" s="5" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="AK38" s="8" t="n">
         <v>0.875</v>
@@ -15823,7 +15823,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="AD39" s="8" t="n">
         <v>0.9895833333333334</v>
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="AJ39" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="AK39" s="8" t="n">
         <v>0.59375</v>
@@ -16010,7 +16010,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>45598</v>
+        <v>45599</v>
       </c>
       <c r="AD40" s="8" t="n">
         <v>0.6770833333333334</v>
@@ -16168,7 +16168,7 @@
         </is>
       </c>
       <c r="AJ40" s="5" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="AK40" s="8" t="n">
         <v>0.5833333333333334</v>
@@ -18202,7 +18202,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -18707,7 +18708,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
